--- a/WRCHOMP.xlsx
+++ b/WRCHOMP.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="47">
   <si>
     <t/>
   </si>
@@ -146,6 +146,12 @@
   </si>
   <si>
     <t>7</t>
+  </si>
+  <si>
+    <t>20143895</t>
+  </si>
+  <si>
+    <t>CHOMP MLO JLY STRW21</t>
   </si>
 </sst>
 </file>
@@ -538,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -761,7 +767,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -781,7 +787,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -801,7 +807,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -901,9 +907,29 @@
         <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
